--- a/stories/arbres/ATOM-SEC.RUE.002-07.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Camille va au square. Elle marche avec papa. Papa est l'adulte. Ils arrivent au bord. Camille donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant. Papa dit : on attend le feu vert. Camille sent la main. Elle reste près de papa. Le feu est vert. Papa dit : feu vert. On avance avec l'adulte. Camille tient la main. Ils marchent ensemble. L'adulte est là. Camille dit : merci papa.</t>
+          <t>Camille va au square. Elle marche avec papa. Papa est l'adulte. Ils arrivent au bord. Camille donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant. On attend le feu vert. Camille sent la main. Elle reste près de papa. Le feu est vert. Feu vert. On avance avec l'adulte. Camille tient la main. Ils marchent ensemble. L'adulte est là. Merci papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Camille va au square. Elle marche avec papa. Papa est l'adulte. Ils arrivent au bord. Camille donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant.
+papa|On attend le feu vert.
+narrateur|Camille sent la main. Elle reste près de papa. Le feu est vert.
+papa|Feu vert. On avance avec l'adulte.
+narrateur|Camille tient la main. Ils marchent ensemble. L'adulte est là.
+enfant-f|Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Camille attend avec papa. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1672,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Camille a donné la main. Elle a attendu le feu vert. Papa, l'adulte, était là. Les pieds sont restés sur le trottoir en attendant.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1843,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Camille serre la main de papa. Ils sentent l'herbe du square.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2010,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2050,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.002-07.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 enfant-f|Merci papa.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1508,7 @@
           <t>narrateur|Camille attend avec papa. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1677,6 +1684,7 @@
           <t>narrateur|Camille a donné la main. Elle a attendu le feu vert. Papa, l'adulte, était là. Les pieds sont restés sur le trottoir en attendant.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1848,6 +1856,7 @@
           <t>narrateur|Camille serre la main de papa. Ils sentent l'herbe du square.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2015,6 +2024,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2033,7 +2043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2057,6 +2067,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2258,6 +2282,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.002-07.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camille attend le feu vert</t>
+          <t>La grille du jardin</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le thym chauffe. Aniss veut poser son bateau dans le bassin du square. À la grille, un arrosoir bascule. Il serre la main, attend le vert.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Camille va au square. Elle marche avec papa. Papa est l'adulte. Ils arrivent au bord. Camille donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant. On attend le feu vert. Camille sent la main. Elle reste près de papa. Le feu est vert. Feu vert. On avance avec l'adulte. Camille tient la main. Ils marchent ensemble. L'adulte est là. Merci papa.</t>
+          <t>Le thym du jardin chauffe au soleil. Une abeille visite une fleur violette. La terre sent le chaud et le vert. Un arrosoir bleu est penché. Aniss tient un bateau de bois. Le bateau sent le copeau neuf. Papa, il flotte ? Oui. Au bassin du square. On y va ? Oui, papa. En ce moment, Aniss essuie la quille. Le bois est lisse, un peu tiède. Tu mets tes chaussures ? Aniss enfile la gauche. Puis la droite. Les lacets font un petit bruit. Tu as fini tes chaussures ? Oui, papa. Papa tend la main. Je prends ta main. Merci, Aniss. Ils passent près des pots d'argile. Le thym frotte le pantalon. La grille de la rue attend, noire. La grille crisse. Oui. Papa ouvre la grille, tout lent. L'arrosoir bascule contre le seuil. Un filet d'eau court vers la bordure. L'eau part ! On reste sur le trottoir. Tu serres ma main ? Aniss serre la main. Ses pieds restent sur le trottoir. L'eau s'arrête dans une fissure. Le bord de la rue est tout proche. Le petit bonhomme est encore rouge. On attend le vert. Aniss regarde le feu piéton. Le bateau tape un peu sa poche. Une voiture passe tout doucement. Il veut flotter. Bientôt. On attend ensemble. Le square sent l'herbe, tout près. Aniss sent le thym sur ses doigts. Ses doigts restent dans la main. Puis le petit bonhomme devient vert. Feu vert. On avance ensemble. Ils marchent, main dans la main. Le portail du square grince. Le bassin brille, tout rond. L'eau ! Tu poses le bateau ? Aniss pose le bateau sur l'eau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Camille va au square. Elle marche avec papa. Papa est l'adulte. Ils arrivent au bord. Camille donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant. Papa dit : on attend le &lt;emphasis level="moderate"&gt;feu&lt;/emphasis&gt; vert. Camille sent la main. Elle reste près de papa. Le feu est vert. Papa dit : feu vert. On avance avec l'adulte. Camille tient la main. Ils marchent ensemble. L'adulte est là. Camille dit : merci papa.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le thym du jardin chauffe au soleil. Une abeille visite une fleur violette. La terre sent le chaud et le vert. Un arrosoir bleu est penché. Aniss tient un bateau de bois. Le bateau sent le copeau neuf. Papa, il flotte ? Oui. Au bassin du square. On y va ? Oui, papa. En ce moment, Aniss essuie la quille. Le bois est lisse, un peu tiède. Tu mets tes chaussures ? Aniss enfile la gauche. Puis la droite. Les lacets font un petit bruit. Tu as fini tes chaussures ? Oui, papa. Papa tend la main. Je prends ta main. Merci, Aniss. Ils passent près des pots d'argile. Le thym frotte le pantalon. La grille de la rue attend, noire. La grille crisse. Oui. Papa ouvre la grille, tout lent. L'arrosoir bascule contre le seuil. Un filet d'eau court vers la bordure. L'eau part ! On reste sur le trottoir. Tu serres ma main ? Aniss serre la main. Ses pieds restent sur le trottoir. L'eau s'arrête dans une fissure. Le bord de la rue est tout proche. Le petit bonhomme est encore rouge. On attend le vert. Aniss regarde le feu piéton. Le bateau tape un peu sa poche. Une voiture passe tout doucement. Il veut flotter. Bientôt. On attend ensemble. Le square sent l'herbe, tout près. Aniss sent le thym sur ses doigts. Ses doigts restent dans la main. Puis le petit bonhomme devient vert. Feu vert. On avance ensemble. Ils marchent, main dans la main. Le portail du square grince. Le bassin brille, tout rond. L'eau ! Tu poses le bateau ? Aniss pose le bateau sur l'eau.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,70 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Camille va au square. Elle marche avec papa. Papa est l'adulte. Ils arrivent au bord. Camille donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant.
-papa|On attend le feu vert.
-narrateur|Camille sent la main. Elle reste près de papa. Le feu est vert.
-papa|Feu vert. On avance avec l'adulte.
-narrateur|Camille tient la main. Ils marchent ensemble. L'adulte est là.
-enfant-f|Merci papa.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le thym du jardin chauffe au soleil.
+narrateur|Une abeille visite une fleur violette.
+narrateur|La terre sent le chaud et le vert.
+narrateur|Un arrosoir bleu est penché.
+narrateur|Aniss tient un bateau de bois.
+narrateur|Le bateau sent le copeau neuf.
+enfant-m|Papa, il flotte ?
+papa|Oui.
+papa|Au bassin du square.
+papa|On y va ?
+enfant-m|Oui, papa.
+narrateur|En ce moment, Aniss essuie la quille.
+narrateur|Le bois est lisse, un peu tiède.
+papa|Tu mets tes chaussures ?
+narrateur|Aniss enfile la gauche.
+narrateur|Puis la droite.
+narrateur|Les lacets font un petit bruit.
+papa|Tu as fini tes chaussures ?
+enfant-m|Oui, papa.
+narrateur|Papa tend la main.
+enfant-m|Je prends ta main.
+papa|Merci, Aniss.
+narrateur|Ils passent près des pots d'argile.
+narrateur|Le thym frotte le pantalon.
+narrateur|La grille de la rue attend, noire.
+enfant-m|La grille crisse.
+papa|Oui.
+narrateur|Papa ouvre la grille, tout lent.
+narrateur|L'arrosoir bascule contre le seuil.
+narrateur|Un filet d'eau court vers la bordure.
+enfant-m|L'eau part !
+papa|On reste sur le trottoir.
+papa|Tu serres ma main ?
+narrateur|Aniss serre la main.
+narrateur|Ses pieds restent sur le trottoir.
+narrateur|L'eau s'arrête dans une fissure.
+narrateur|Le bord de la rue est tout proche.
+narrateur|Le petit bonhomme est encore rouge.
+papa|On attend le vert.
+narrateur|Aniss regarde le feu piéton.
+narrateur|Le bateau tape un peu sa poche.
+narrateur|Une voiture passe tout doucement.
+enfant-m|Il veut flotter.
+papa|Bientôt.
+papa|On attend ensemble.
+narrateur|Le square sent l'herbe, tout près.
+narrateur|Aniss sent le thym sur ses doigts.
+narrateur|Ses doigts restent dans la main.
+narrateur|Puis le petit bonhomme devient vert.
+papa|Feu vert.
+papa|On avance ensemble.
+narrateur|Ils marchent, main dans la main.
+narrateur|Le portail du square grince.
+narrateur|Le bassin brille, tout rond.
+enfant-m|L'eau !
+papa|Tu poses le bateau ?
+narrateur|Aniss pose le bateau sur l'eau.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,12 +1412,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Camille attend avec papa. Que fait-elle ?</t>
+          <t>Aniss attend avec papa. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Camille attend avec papa. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss attend avec papa. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1365,7 +1432,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>feu vert | la main | avec papa | avec l'adulte | attendre</t>
+          <t>feu vert | la main | avec maman | avec papa | avec l'adulte | attendre | le vert</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1380,7 +1447,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle donne la main. Elle attend le feu vert. Que fait Camille ?</t>
+          <t>Il serre la main. Il attend le feu vert. Que fait Aniss ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1429,7 +1496,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1505,10 +1572,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Camille attend avec papa. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Aniss attend avec papa.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,12 +1600,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Camille a donné la main. Elle a attendu le feu vert. Papa, l'adulte, était là. Les pieds sont restés sur le trottoir en attendant.</t>
+          <t>Aniss a serré la main. Il a attendu le feu vert. Ses pieds restaient sur le trottoir. Tu as attendu le vert ? Oui, papa. L'arrosoir dort contre le seuil. Le bateau avance, tout lent.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Camille a donné la main. Elle a attendu le &lt;emphasis level="moderate"&gt;feu&lt;/emphasis&gt; vert. Papa, l'adulte, était là. Les pieds sont restés sur le trottoir en attendant.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a serré la main. Il a attendu le feu vert. Ses pieds restaient sur le trottoir. Tu as attendu le vert ? Oui, papa. L'arrosoir dort contre le seuil. Le bateau avance, tout lent.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1594,14 +1661,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1681,10 +1748,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Camille a donné la main. Elle a attendu le feu vert. Papa, l'adulte, était là. Les pieds sont restés sur le trottoir en attendant.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Aniss a serré la main.
+narrateur|Il a attendu le feu vert.
+narrateur|Ses pieds restaient sur le trottoir.
+papa|Tu as attendu le vert ?
+enfant-m|Oui, papa.
+narrateur|L'arrosoir dort contre le seuil.
+narrateur|Le bateau avance, tout lent.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1709,12 +1781,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Camille serre la main de papa. Ils sentent l'herbe du square.</t>
+          <t>Le bateau fait un petit sillage. Aniss souffle, tout doux. L'eau sent le soleil et la pierre. Il flotte ! Oui. Tu le rattrapes au bord ? Aniss le prend au rebord du bassin. Le bois est mouillé, plus foncé. Une feuille tourne sur l'eau. Encore. On le pose encore ? Oui. Le bateau repart, tout fier. Les mains d'Aniss sentent le thym.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Camille serre la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de papa. Ils sentent l'herbe du square.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bateau fait un petit sillage. Aniss souffle, tout doux. L'eau sent le soleil et la pierre. Il flotte ! Oui. Tu le rattrapes au bord ? Aniss le prend au rebord du bassin. Le bois est mouillé, plus foncé. Une feuille tourne sur l'eau. Encore. On le pose encore ? Oui. Le bateau repart, tout fier. Les mains d'Aniss sentent le thym.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1770,14 +1842,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1853,10 +1925,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Camille serre la main de papa. Ils sentent l'herbe du square.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le bateau fait un petit sillage.
+narrateur|Aniss souffle, tout doux.
+narrateur|L'eau sent le soleil et la pierre.
+enfant-m|Il flotte !
+papa|Oui.
+papa|Tu le rattrapes au bord ?
+narrateur|Aniss le prend au rebord du bassin.
+narrateur|Le bois est mouillé, plus foncé.
+narrateur|Une feuille tourne sur l'eau.
+enfant-m|Encore.
+papa|On le pose encore ?
+enfant-m|Oui.
+narrateur|Le bateau repart, tout fier.
+narrateur|Les mains d'Aniss sentent le thym.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1881,12 +1965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss essuie le bateau sur son genou. Une goutte tombe dans le bassin. Il a voyagé. Oui. Le thym du jardin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss essuie le bateau sur son genou. Une goutte tombe dans le bassin. Il a voyagé. Oui. Le thym du jardin sent encore le soleil.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1942,14 +2026,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2021,10 +2105,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Aniss essuie le bateau sur son genou.
+narrateur|Une goutte tombe dans le bassin.
+enfant-m|Il a voyagé.
+papa|Oui.
+narrateur|Le thym du jardin sent encore le soleil.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2043,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2081,6 +2168,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.002-07.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trajet vers le square</t>
+          <t>jardin puis grille de la rue vers le square</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Camille, papa</t>
+          <t>Aniss, papa</t>
         </is>
       </c>
     </row>
